--- a/report_cleansing_ps.xlsx
+++ b/report_cleansing_ps.xlsx
@@ -8029,7 +8029,7 @@
         <v>2281</v>
       </c>
       <c r="J25" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -8464,7 +8464,7 @@
         <v>2276</v>
       </c>
       <c r="J40" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -8609,7 +8609,7 @@
         <v>2276</v>
       </c>
       <c r="J45" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -8783,7 +8783,7 @@
         <v>2276</v>
       </c>
       <c r="J51" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -8841,7 +8841,7 @@
         <v>2274</v>
       </c>
       <c r="J53" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -10001,7 +10001,7 @@
         <v>2274</v>
       </c>
       <c r="J93" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -11045,7 +11045,7 @@
         <v>2278</v>
       </c>
       <c r="J129" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -11190,7 +11190,7 @@
         <v>2274</v>
       </c>
       <c r="J134" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -12698,7 +12698,7 @@
         <v>2274</v>
       </c>
       <c r="J186" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -12901,7 +12901,7 @@
         <v>2273</v>
       </c>
       <c r="J193" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="194" spans="1:10">
@@ -12988,7 +12988,7 @@
         <v>2276</v>
       </c>
       <c r="J196" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -13017,7 +13017,7 @@
         <v>2276</v>
       </c>
       <c r="J197" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="198" spans="1:10">
@@ -13829,7 +13829,7 @@
         <v>2273</v>
       </c>
       <c r="J225" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -14090,7 +14090,7 @@
         <v>2276</v>
       </c>
       <c r="J234" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -14380,7 +14380,7 @@
         <v>2273</v>
       </c>
       <c r="J244" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -15395,7 +15395,7 @@
         <v>2274</v>
       </c>
       <c r="J279" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="280" spans="1:10">
@@ -15424,7 +15424,7 @@
         <v>2276</v>
       </c>
       <c r="J280" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="281" spans="1:10">
@@ -15453,7 +15453,7 @@
         <v>2276</v>
       </c>
       <c r="J281" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="282" spans="1:10">
@@ -15569,7 +15569,7 @@
         <v>2276</v>
       </c>
       <c r="J285" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="286" spans="1:10">
@@ -16091,7 +16091,7 @@
         <v>2274</v>
       </c>
       <c r="J303" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -16758,7 +16758,7 @@
         <v>2274</v>
       </c>
       <c r="J326" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="327" spans="1:10">
@@ -17086,7 +17086,7 @@
         <v>2285</v>
       </c>
       <c r="J337" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="338" spans="1:10">
@@ -17455,7 +17455,7 @@
         <v>2290</v>
       </c>
       <c r="J349" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="350" spans="1:10">
@@ -17667,7 +17667,7 @@
         <v>2292</v>
       </c>
       <c r="J356" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="357" spans="1:10">
@@ -18074,7 +18074,7 @@
         <v>2282</v>
       </c>
       <c r="J369" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="370" spans="1:10">
@@ -18132,7 +18132,7 @@
         <v>2292</v>
       </c>
       <c r="J371" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="372" spans="1:10">
@@ -18646,7 +18646,7 @@
         <v>2257</v>
       </c>
       <c r="J388" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -19102,7 +19102,7 @@
         <v>2297</v>
       </c>
       <c r="J403" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="404" spans="1:10">
@@ -19262,7 +19262,7 @@
         <v>2282</v>
       </c>
       <c r="J408" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="409" spans="1:10">
@@ -19326,7 +19326,7 @@
         <v>2282</v>
       </c>
       <c r="J410" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="411" spans="1:10">
@@ -19817,7 +19817,7 @@
         <v>2282</v>
       </c>
       <c r="J426" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="427" spans="1:10">
@@ -19881,7 +19881,7 @@
         <v>2284</v>
       </c>
       <c r="J428" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -20003,7 +20003,7 @@
         <v>2297</v>
       </c>
       <c r="J432" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -20183,7 +20183,7 @@
         <v>2303</v>
       </c>
       <c r="J438" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="439" spans="1:10">
@@ -20308,7 +20308,7 @@
         <v>2288</v>
       </c>
       <c r="J442" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="443" spans="1:10">
@@ -21484,7 +21484,7 @@
         <v>2296</v>
       </c>
       <c r="J481" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="482" spans="1:10">
@@ -21577,7 +21577,7 @@
         <v>2257</v>
       </c>
       <c r="J484" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="485" spans="1:10">
@@ -21609,7 +21609,7 @@
         <v>2288</v>
       </c>
       <c r="J485" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="486" spans="1:10">
@@ -21763,7 +21763,7 @@
         <v>2291</v>
       </c>
       <c r="J490" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="491" spans="1:10">
@@ -21911,7 +21911,7 @@
         <v>2292</v>
       </c>
       <c r="J495" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="496" spans="1:10">
@@ -22033,7 +22033,7 @@
         <v>2257</v>
       </c>
       <c r="J499" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="500" spans="1:10">
@@ -22210,7 +22210,7 @@
         <v>2287</v>
       </c>
       <c r="J505" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="506" spans="1:10">
@@ -22358,7 +22358,7 @@
         <v>2299</v>
       </c>
       <c r="J510" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="511" spans="1:10">
@@ -22541,7 +22541,7 @@
         <v>2282</v>
       </c>
       <c r="J516" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="517" spans="1:10">
@@ -22959,7 +22959,7 @@
         <v>2301</v>
       </c>
       <c r="J530" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="531" spans="1:10">
@@ -23203,7 +23203,7 @@
         <v>2299</v>
       </c>
       <c r="J538" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="539" spans="1:10">
@@ -23409,7 +23409,7 @@
         <v>2291</v>
       </c>
       <c r="J545" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="546" spans="1:10">
@@ -23653,7 +23653,7 @@
         <v>2292</v>
       </c>
       <c r="J553" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="554" spans="1:10">
@@ -24199,7 +24199,7 @@
         <v>2296</v>
       </c>
       <c r="J571" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="572" spans="1:10">
@@ -24231,7 +24231,7 @@
         <v>2300</v>
       </c>
       <c r="J572" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="573" spans="1:10">
@@ -24510,7 +24510,7 @@
         <v>2288</v>
       </c>
       <c r="J581" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="582" spans="1:10">
@@ -24632,7 +24632,7 @@
         <v>2305</v>
       </c>
       <c r="J585" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="586" spans="1:10">
@@ -24754,7 +24754,7 @@
         <v>2272</v>
       </c>
       <c r="J589" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="590" spans="1:10">
@@ -24844,7 +24844,7 @@
         <v>2284</v>
       </c>
       <c r="J592" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="593" spans="1:10">
@@ -24873,7 +24873,7 @@
         <v>2297</v>
       </c>
       <c r="J593" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="594" spans="1:10">
@@ -24992,7 +24992,7 @@
         <v>2299</v>
       </c>
       <c r="J597" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="598" spans="1:10">
@@ -25143,7 +25143,7 @@
         <v>2307</v>
       </c>
       <c r="J602" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="603" spans="1:10">
@@ -25265,7 +25265,7 @@
         <v>2290</v>
       </c>
       <c r="J606" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="607" spans="1:10">
@@ -25326,7 +25326,7 @@
         <v>2299</v>
       </c>
       <c r="J608" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="609" spans="1:10">
@@ -25477,7 +25477,7 @@
         <v>2290</v>
       </c>
       <c r="J613" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="614" spans="1:10">
@@ -25538,7 +25538,7 @@
         <v>2290</v>
       </c>
       <c r="J615" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="616" spans="1:10">
@@ -25599,7 +25599,7 @@
         <v>2295</v>
       </c>
       <c r="J617" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="618" spans="1:10">
@@ -25631,7 +25631,7 @@
         <v>2272</v>
       </c>
       <c r="J618" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="619" spans="1:10">
@@ -26456,7 +26456,7 @@
         <v>2257</v>
       </c>
       <c r="J645" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="646" spans="1:10">
@@ -26610,7 +26610,7 @@
         <v>2284</v>
       </c>
       <c r="J650" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="651" spans="1:10">
@@ -26671,7 +26671,7 @@
         <v>2287</v>
       </c>
       <c r="J652" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="653" spans="1:10">
@@ -27565,7 +27565,7 @@
         <v>2301</v>
       </c>
       <c r="J682" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="683" spans="1:10">
@@ -27777,7 +27777,7 @@
         <v>2284</v>
       </c>
       <c r="J689" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="690" spans="1:10">
@@ -27899,7 +27899,7 @@
         <v>2284</v>
       </c>
       <c r="J693" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="694" spans="1:10">
@@ -28082,7 +28082,7 @@
         <v>2297</v>
       </c>
       <c r="J699" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="700" spans="1:10">
@@ -28111,7 +28111,7 @@
         <v>2295</v>
       </c>
       <c r="J700" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="701" spans="1:10">
@@ -28172,7 +28172,7 @@
         <v>2295</v>
       </c>
       <c r="J702" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="703" spans="1:10">
@@ -28605,7 +28605,7 @@
         <v>2284</v>
       </c>
       <c r="J716" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="717" spans="1:10">
@@ -29047,7 +29047,7 @@
         <v>2284</v>
       </c>
       <c r="J730" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="731" spans="1:10">
@@ -29140,7 +29140,7 @@
         <v>2297</v>
       </c>
       <c r="J733" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="734" spans="1:10">
@@ -29381,7 +29381,7 @@
         <v>2295</v>
       </c>
       <c r="J741" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="742" spans="1:10">
@@ -29532,7 +29532,7 @@
         <v>2286</v>
       </c>
       <c r="J746" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="747" spans="1:10">
@@ -29718,7 +29718,7 @@
         <v>2282</v>
       </c>
       <c r="J752" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="753" spans="1:10">
@@ -29808,7 +29808,7 @@
         <v>2304</v>
       </c>
       <c r="J755" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="756" spans="1:10">
@@ -30084,7 +30084,7 @@
         <v>2295</v>
       </c>
       <c r="J764" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="765" spans="1:10">
@@ -30113,7 +30113,7 @@
         <v>2295</v>
       </c>
       <c r="J765" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="766" spans="1:10">
@@ -30424,7 +30424,7 @@
         <v>2288</v>
       </c>
       <c r="J775" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="776" spans="1:10">
@@ -30636,7 +30636,7 @@
         <v>2292</v>
       </c>
       <c r="J782" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="783" spans="1:10">
@@ -30851,7 +30851,7 @@
         <v>2303</v>
       </c>
       <c r="J789" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="790" spans="1:10">
@@ -31095,7 +31095,7 @@
         <v>2298</v>
       </c>
       <c r="J797" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="798" spans="1:10">
@@ -31182,7 +31182,7 @@
         <v>2291</v>
       </c>
       <c r="J800" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="801" spans="1:10">

--- a/report_cleansing_ps.xlsx
+++ b/report_cleansing_ps.xlsx
@@ -8029,7 +8029,7 @@
         <v>2281</v>
       </c>
       <c r="J25" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -8464,7 +8464,7 @@
         <v>2276</v>
       </c>
       <c r="J40" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -8609,7 +8609,7 @@
         <v>2276</v>
       </c>
       <c r="J45" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -8783,7 +8783,7 @@
         <v>2276</v>
       </c>
       <c r="J51" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -8841,7 +8841,7 @@
         <v>2274</v>
       </c>
       <c r="J53" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -10001,7 +10001,7 @@
         <v>2274</v>
       </c>
       <c r="J93" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -11045,7 +11045,7 @@
         <v>2278</v>
       </c>
       <c r="J129" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -11190,7 +11190,7 @@
         <v>2274</v>
       </c>
       <c r="J134" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -12321,7 +12321,7 @@
         <v>2274</v>
       </c>
       <c r="J173" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -12698,7 +12698,7 @@
         <v>2274</v>
       </c>
       <c r="J186" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -12901,7 +12901,7 @@
         <v>2273</v>
       </c>
       <c r="J193" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="194" spans="1:10">
@@ -12988,7 +12988,7 @@
         <v>2276</v>
       </c>
       <c r="J196" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -13017,7 +13017,7 @@
         <v>2276</v>
       </c>
       <c r="J197" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="198" spans="1:10">
@@ -13829,7 +13829,7 @@
         <v>2273</v>
       </c>
       <c r="J225" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -14090,7 +14090,7 @@
         <v>2276</v>
       </c>
       <c r="J234" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -14380,7 +14380,7 @@
         <v>2273</v>
       </c>
       <c r="J244" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -15395,7 +15395,7 @@
         <v>2274</v>
       </c>
       <c r="J279" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="280" spans="1:10">
@@ -15424,7 +15424,7 @@
         <v>2276</v>
       </c>
       <c r="J280" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="281" spans="1:10">
@@ -15453,7 +15453,7 @@
         <v>2276</v>
       </c>
       <c r="J281" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="282" spans="1:10">
@@ -15569,7 +15569,7 @@
         <v>2276</v>
       </c>
       <c r="J285" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="286" spans="1:10">
@@ -16091,7 +16091,7 @@
         <v>2274</v>
       </c>
       <c r="J303" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -16758,7 +16758,7 @@
         <v>2274</v>
       </c>
       <c r="J326" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="327" spans="1:10">
@@ -17086,7 +17086,7 @@
         <v>2285</v>
       </c>
       <c r="J337" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="338" spans="1:10">
@@ -17455,7 +17455,7 @@
         <v>2290</v>
       </c>
       <c r="J349" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="350" spans="1:10">
@@ -17667,7 +17667,7 @@
         <v>2292</v>
       </c>
       <c r="J356" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="357" spans="1:10">
@@ -18074,7 +18074,7 @@
         <v>2282</v>
       </c>
       <c r="J369" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="370" spans="1:10">
@@ -18132,7 +18132,7 @@
         <v>2292</v>
       </c>
       <c r="J371" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="372" spans="1:10">
@@ -18646,7 +18646,7 @@
         <v>2257</v>
       </c>
       <c r="J388" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -19102,7 +19102,7 @@
         <v>2297</v>
       </c>
       <c r="J403" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="404" spans="1:10">
@@ -19262,7 +19262,7 @@
         <v>2282</v>
       </c>
       <c r="J408" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="409" spans="1:10">
@@ -19326,7 +19326,7 @@
         <v>2282</v>
       </c>
       <c r="J410" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="411" spans="1:10">
@@ -19817,7 +19817,7 @@
         <v>2282</v>
       </c>
       <c r="J426" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="427" spans="1:10">
@@ -19881,7 +19881,7 @@
         <v>2284</v>
       </c>
       <c r="J428" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -20003,7 +20003,7 @@
         <v>2297</v>
       </c>
       <c r="J432" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -20183,7 +20183,7 @@
         <v>2303</v>
       </c>
       <c r="J438" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="439" spans="1:10">
@@ -20308,7 +20308,7 @@
         <v>2288</v>
       </c>
       <c r="J442" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="443" spans="1:10">
@@ -21484,7 +21484,7 @@
         <v>2296</v>
       </c>
       <c r="J481" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="482" spans="1:10">
@@ -21577,7 +21577,7 @@
         <v>2257</v>
       </c>
       <c r="J484" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="485" spans="1:10">
@@ -21609,7 +21609,7 @@
         <v>2288</v>
       </c>
       <c r="J485" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="486" spans="1:10">
@@ -21763,7 +21763,7 @@
         <v>2291</v>
       </c>
       <c r="J490" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="491" spans="1:10">
@@ -21911,7 +21911,7 @@
         <v>2292</v>
       </c>
       <c r="J495" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="496" spans="1:10">
@@ -22033,7 +22033,7 @@
         <v>2257</v>
       </c>
       <c r="J499" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="500" spans="1:10">
@@ -22210,7 +22210,7 @@
         <v>2287</v>
       </c>
       <c r="J505" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="506" spans="1:10">
@@ -22358,7 +22358,7 @@
         <v>2299</v>
       </c>
       <c r="J510" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="511" spans="1:10">
@@ -22541,7 +22541,7 @@
         <v>2282</v>
       </c>
       <c r="J516" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="517" spans="1:10">
@@ -22959,7 +22959,7 @@
         <v>2301</v>
       </c>
       <c r="J530" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="531" spans="1:10">
@@ -23203,7 +23203,7 @@
         <v>2299</v>
       </c>
       <c r="J538" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="539" spans="1:10">
@@ -23409,7 +23409,7 @@
         <v>2291</v>
       </c>
       <c r="J545" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="546" spans="1:10">
@@ -23653,7 +23653,7 @@
         <v>2292</v>
       </c>
       <c r="J553" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="554" spans="1:10">
@@ -24167,7 +24167,7 @@
         <v>2292</v>
       </c>
       <c r="J570" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="571" spans="1:10">
@@ -24199,7 +24199,7 @@
         <v>2296</v>
       </c>
       <c r="J571" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="572" spans="1:10">
@@ -24231,7 +24231,7 @@
         <v>2300</v>
       </c>
       <c r="J572" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="573" spans="1:10">
@@ -24510,7 +24510,7 @@
         <v>2288</v>
       </c>
       <c r="J581" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="582" spans="1:10">
@@ -24632,7 +24632,7 @@
         <v>2305</v>
       </c>
       <c r="J585" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="586" spans="1:10">
@@ -24754,7 +24754,7 @@
         <v>2272</v>
       </c>
       <c r="J589" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="590" spans="1:10">
@@ -24844,7 +24844,7 @@
         <v>2284</v>
       </c>
       <c r="J592" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="593" spans="1:10">
@@ -24873,7 +24873,7 @@
         <v>2297</v>
       </c>
       <c r="J593" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="594" spans="1:10">
@@ -24992,7 +24992,7 @@
         <v>2299</v>
       </c>
       <c r="J597" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="598" spans="1:10">
@@ -25143,7 +25143,7 @@
         <v>2307</v>
       </c>
       <c r="J602" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="603" spans="1:10">
@@ -25265,7 +25265,7 @@
         <v>2290</v>
       </c>
       <c r="J606" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="607" spans="1:10">
@@ -25326,7 +25326,7 @@
         <v>2299</v>
       </c>
       <c r="J608" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="609" spans="1:10">
@@ -25477,7 +25477,7 @@
         <v>2290</v>
       </c>
       <c r="J613" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="614" spans="1:10">
@@ -25538,7 +25538,7 @@
         <v>2290</v>
       </c>
       <c r="J615" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="616" spans="1:10">
@@ -25599,7 +25599,7 @@
         <v>2295</v>
       </c>
       <c r="J617" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="618" spans="1:10">
@@ -25631,7 +25631,7 @@
         <v>2272</v>
       </c>
       <c r="J618" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="619" spans="1:10">
@@ -26456,7 +26456,7 @@
         <v>2257</v>
       </c>
       <c r="J645" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="646" spans="1:10">
@@ -26610,7 +26610,7 @@
         <v>2284</v>
       </c>
       <c r="J650" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="651" spans="1:10">
@@ -26671,7 +26671,7 @@
         <v>2287</v>
       </c>
       <c r="J652" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="653" spans="1:10">
@@ -27565,7 +27565,7 @@
         <v>2301</v>
       </c>
       <c r="J682" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="683" spans="1:10">
@@ -27777,7 +27777,7 @@
         <v>2284</v>
       </c>
       <c r="J689" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="690" spans="1:10">
@@ -27899,7 +27899,7 @@
         <v>2284</v>
       </c>
       <c r="J693" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="694" spans="1:10">
@@ -28082,7 +28082,7 @@
         <v>2297</v>
       </c>
       <c r="J699" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="700" spans="1:10">
@@ -28111,7 +28111,7 @@
         <v>2295</v>
       </c>
       <c r="J700" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="701" spans="1:10">
@@ -28172,7 +28172,7 @@
         <v>2295</v>
       </c>
       <c r="J702" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="703" spans="1:10">
@@ -28605,7 +28605,7 @@
         <v>2284</v>
       </c>
       <c r="J716" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="717" spans="1:10">
@@ -29047,7 +29047,7 @@
         <v>2284</v>
       </c>
       <c r="J730" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="731" spans="1:10">
@@ -29140,7 +29140,7 @@
         <v>2297</v>
       </c>
       <c r="J733" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="734" spans="1:10">
@@ -29381,7 +29381,7 @@
         <v>2295</v>
       </c>
       <c r="J741" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="742" spans="1:10">
@@ -29532,7 +29532,7 @@
         <v>2286</v>
       </c>
       <c r="J746" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="747" spans="1:10">
@@ -29718,7 +29718,7 @@
         <v>2282</v>
       </c>
       <c r="J752" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="753" spans="1:10">
@@ -29808,7 +29808,7 @@
         <v>2304</v>
       </c>
       <c r="J755" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="756" spans="1:10">
@@ -30084,7 +30084,7 @@
         <v>2295</v>
       </c>
       <c r="J764" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="765" spans="1:10">
@@ -30113,7 +30113,7 @@
         <v>2295</v>
       </c>
       <c r="J765" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="766" spans="1:10">
@@ -30424,7 +30424,7 @@
         <v>2288</v>
       </c>
       <c r="J775" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="776" spans="1:10">
@@ -30636,7 +30636,7 @@
         <v>2292</v>
       </c>
       <c r="J782" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="783" spans="1:10">
@@ -30851,7 +30851,7 @@
         <v>2303</v>
       </c>
       <c r="J789" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="790" spans="1:10">
@@ -31095,7 +31095,7 @@
         <v>2298</v>
       </c>
       <c r="J797" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="798" spans="1:10">
@@ -31182,7 +31182,7 @@
         <v>2291</v>
       </c>
       <c r="J800" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="801" spans="1:10">

--- a/report_cleansing_ps.xlsx
+++ b/report_cleansing_ps.xlsx
@@ -8029,7 +8029,7 @@
         <v>2281</v>
       </c>
       <c r="J25" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -8319,7 +8319,7 @@
         <v>2279</v>
       </c>
       <c r="J35" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -8464,7 +8464,7 @@
         <v>2276</v>
       </c>
       <c r="J40" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -8783,7 +8783,7 @@
         <v>2276</v>
       </c>
       <c r="J51" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -8841,7 +8841,7 @@
         <v>2274</v>
       </c>
       <c r="J53" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -9334,7 +9334,7 @@
         <v>2274</v>
       </c>
       <c r="J70" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -9885,7 +9885,7 @@
         <v>2279</v>
       </c>
       <c r="J89" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -10001,7 +10001,7 @@
         <v>2274</v>
       </c>
       <c r="J93" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -10987,7 +10987,7 @@
         <v>2279</v>
       </c>
       <c r="J127" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -11045,7 +11045,7 @@
         <v>2278</v>
       </c>
       <c r="J129" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -11190,7 +11190,7 @@
         <v>2274</v>
       </c>
       <c r="J134" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -11306,7 +11306,7 @@
         <v>2274</v>
       </c>
       <c r="J138" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -11683,7 +11683,7 @@
         <v>2279</v>
       </c>
       <c r="J151" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -12263,7 +12263,7 @@
         <v>2277</v>
       </c>
       <c r="J171" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -12582,7 +12582,7 @@
         <v>2274</v>
       </c>
       <c r="J182" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -12698,7 +12698,7 @@
         <v>2274</v>
       </c>
       <c r="J186" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -12901,7 +12901,7 @@
         <v>2273</v>
       </c>
       <c r="J193" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="194" spans="1:10">
@@ -12988,7 +12988,7 @@
         <v>2276</v>
       </c>
       <c r="J196" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -13017,7 +13017,7 @@
         <v>2276</v>
       </c>
       <c r="J197" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="198" spans="1:10">
@@ -13336,7 +13336,7 @@
         <v>2274</v>
       </c>
       <c r="J208" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -13568,7 +13568,7 @@
         <v>2274</v>
       </c>
       <c r="J216" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -13742,7 +13742,7 @@
         <v>2279</v>
       </c>
       <c r="J222" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -13829,7 +13829,7 @@
         <v>2273</v>
       </c>
       <c r="J225" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -14032,7 +14032,7 @@
         <v>2274</v>
       </c>
       <c r="J232" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -14090,7 +14090,7 @@
         <v>2276</v>
       </c>
       <c r="J234" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -14322,7 +14322,7 @@
         <v>2274</v>
       </c>
       <c r="J242" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="243" spans="1:10">
@@ -14380,7 +14380,7 @@
         <v>2273</v>
       </c>
       <c r="J244" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -14496,7 +14496,7 @@
         <v>2277</v>
       </c>
       <c r="J248" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="249" spans="1:10">
@@ -15076,7 +15076,7 @@
         <v>2277</v>
       </c>
       <c r="J268" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="269" spans="1:10">
@@ -15192,7 +15192,7 @@
         <v>2277</v>
       </c>
       <c r="J272" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="273" spans="1:10">
@@ -15279,7 +15279,7 @@
         <v>2274</v>
       </c>
       <c r="J275" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="276" spans="1:10">
@@ -15395,7 +15395,7 @@
         <v>2274</v>
       </c>
       <c r="J279" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="280" spans="1:10">
@@ -15424,7 +15424,7 @@
         <v>2276</v>
       </c>
       <c r="J280" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="281" spans="1:10">
@@ -15453,7 +15453,7 @@
         <v>2276</v>
       </c>
       <c r="J281" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="282" spans="1:10">
@@ -15569,7 +15569,7 @@
         <v>2276</v>
       </c>
       <c r="J285" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="286" spans="1:10">
@@ -15598,7 +15598,7 @@
         <v>2274</v>
       </c>
       <c r="J286" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="287" spans="1:10">
@@ -16091,7 +16091,7 @@
         <v>2274</v>
       </c>
       <c r="J303" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -16352,7 +16352,7 @@
         <v>2274</v>
       </c>
       <c r="J312" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="313" spans="1:10">
@@ -16758,7 +16758,7 @@
         <v>2274</v>
       </c>
       <c r="J326" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="327" spans="1:10">
@@ -17086,7 +17086,7 @@
         <v>2285</v>
       </c>
       <c r="J337" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="338" spans="1:10">
@@ -17275,7 +17275,7 @@
         <v>2288</v>
       </c>
       <c r="J343" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="344" spans="1:10">
@@ -17307,7 +17307,7 @@
         <v>2282</v>
       </c>
       <c r="J344" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="345" spans="1:10">
@@ -17455,7 +17455,7 @@
         <v>2290</v>
       </c>
       <c r="J349" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="350" spans="1:10">
@@ -17487,7 +17487,7 @@
         <v>2288</v>
       </c>
       <c r="J350" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="351" spans="1:10">
@@ -18074,7 +18074,7 @@
         <v>2282</v>
       </c>
       <c r="J369" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="370" spans="1:10">
@@ -18559,7 +18559,7 @@
         <v>2282</v>
       </c>
       <c r="J385" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -18588,7 +18588,7 @@
         <v>2292</v>
       </c>
       <c r="J386" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -18646,7 +18646,7 @@
         <v>2257</v>
       </c>
       <c r="J388" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -19102,7 +19102,7 @@
         <v>2297</v>
       </c>
       <c r="J403" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="404" spans="1:10">
@@ -19262,7 +19262,7 @@
         <v>2282</v>
       </c>
       <c r="J408" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="409" spans="1:10">
@@ -19326,7 +19326,7 @@
         <v>2282</v>
       </c>
       <c r="J410" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="411" spans="1:10">
@@ -19634,7 +19634,7 @@
         <v>2282</v>
       </c>
       <c r="J420" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="421" spans="1:10">
@@ -19817,7 +19817,7 @@
         <v>2282</v>
       </c>
       <c r="J426" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="427" spans="1:10">
@@ -19881,7 +19881,7 @@
         <v>2284</v>
       </c>
       <c r="J428" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -19913,7 +19913,7 @@
         <v>2284</v>
       </c>
       <c r="J429" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -20003,7 +20003,7 @@
         <v>2297</v>
       </c>
       <c r="J432" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -20122,7 +20122,7 @@
         <v>2299</v>
       </c>
       <c r="J436" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="437" spans="1:10">
@@ -20276,7 +20276,7 @@
         <v>2284</v>
       </c>
       <c r="J441" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="442" spans="1:10">
@@ -20613,7 +20613,7 @@
         <v>2304</v>
       </c>
       <c r="J452" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="453" spans="1:10">
@@ -21484,7 +21484,7 @@
         <v>2296</v>
       </c>
       <c r="J481" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="482" spans="1:10">
@@ -21577,7 +21577,7 @@
         <v>2257</v>
       </c>
       <c r="J484" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="485" spans="1:10">
@@ -21734,7 +21734,7 @@
         <v>2304</v>
       </c>
       <c r="J489" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="490" spans="1:10">
@@ -21763,7 +21763,7 @@
         <v>2291</v>
       </c>
       <c r="J490" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="491" spans="1:10">
@@ -21911,7 +21911,7 @@
         <v>2292</v>
       </c>
       <c r="J495" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="496" spans="1:10">
@@ -22033,7 +22033,7 @@
         <v>2257</v>
       </c>
       <c r="J499" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="500" spans="1:10">
@@ -22210,7 +22210,7 @@
         <v>2287</v>
       </c>
       <c r="J505" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="506" spans="1:10">
@@ -22358,7 +22358,7 @@
         <v>2299</v>
       </c>
       <c r="J510" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="511" spans="1:10">
@@ -22541,7 +22541,7 @@
         <v>2282</v>
       </c>
       <c r="J516" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="517" spans="1:10">
@@ -22573,7 +22573,7 @@
         <v>2284</v>
       </c>
       <c r="J517" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="518" spans="1:10">
@@ -22808,7 +22808,7 @@
         <v>2292</v>
       </c>
       <c r="J525" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="526" spans="1:10">
@@ -22840,7 +22840,7 @@
         <v>2288</v>
       </c>
       <c r="J526" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="527" spans="1:10">
@@ -22959,7 +22959,7 @@
         <v>2301</v>
       </c>
       <c r="J530" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="531" spans="1:10">
@@ -23203,7 +23203,7 @@
         <v>2299</v>
       </c>
       <c r="J538" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="539" spans="1:10">
@@ -23293,7 +23293,7 @@
         <v>2299</v>
       </c>
       <c r="J541" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="542" spans="1:10">
@@ -23409,7 +23409,7 @@
         <v>2291</v>
       </c>
       <c r="J545" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="546" spans="1:10">
@@ -23653,7 +23653,7 @@
         <v>2292</v>
       </c>
       <c r="J553" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="554" spans="1:10">
@@ -24199,7 +24199,7 @@
         <v>2296</v>
       </c>
       <c r="J571" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="572" spans="1:10">
@@ -24231,7 +24231,7 @@
         <v>2300</v>
       </c>
       <c r="J572" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="573" spans="1:10">
@@ -24295,7 +24295,7 @@
         <v>2282</v>
       </c>
       <c r="J574" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="575" spans="1:10">
@@ -24356,7 +24356,7 @@
         <v>2282</v>
       </c>
       <c r="J576" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="577" spans="1:10">
@@ -24510,7 +24510,7 @@
         <v>2288</v>
       </c>
       <c r="J581" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="582" spans="1:10">
@@ -24632,7 +24632,7 @@
         <v>2305</v>
       </c>
       <c r="J585" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="586" spans="1:10">
@@ -24690,7 +24690,7 @@
         <v>2295</v>
       </c>
       <c r="J587" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="588" spans="1:10">
@@ -24754,7 +24754,7 @@
         <v>2272</v>
       </c>
       <c r="J589" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="590" spans="1:10">
@@ -24844,7 +24844,7 @@
         <v>2284</v>
       </c>
       <c r="J592" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="593" spans="1:10">
@@ -24873,7 +24873,7 @@
         <v>2297</v>
       </c>
       <c r="J593" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="594" spans="1:10">
@@ -24992,7 +24992,7 @@
         <v>2299</v>
       </c>
       <c r="J597" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="598" spans="1:10">
@@ -25143,7 +25143,7 @@
         <v>2307</v>
       </c>
       <c r="J602" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="603" spans="1:10">
@@ -25265,7 +25265,7 @@
         <v>2290</v>
       </c>
       <c r="J606" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="607" spans="1:10">
@@ -25297,7 +25297,7 @@
         <v>2282</v>
       </c>
       <c r="J607" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="608" spans="1:10">
@@ -25326,7 +25326,7 @@
         <v>2299</v>
       </c>
       <c r="J608" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="609" spans="1:10">
@@ -25448,7 +25448,7 @@
         <v>2304</v>
       </c>
       <c r="J612" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="613" spans="1:10">
@@ -25477,7 +25477,7 @@
         <v>2290</v>
       </c>
       <c r="J613" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="614" spans="1:10">
@@ -25509,7 +25509,7 @@
         <v>2284</v>
       </c>
       <c r="J614" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="615" spans="1:10">
@@ -25538,7 +25538,7 @@
         <v>2290</v>
       </c>
       <c r="J615" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="616" spans="1:10">
@@ -25599,7 +25599,7 @@
         <v>2295</v>
       </c>
       <c r="J617" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="618" spans="1:10">
@@ -25631,7 +25631,7 @@
         <v>2272</v>
       </c>
       <c r="J618" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="619" spans="1:10">
@@ -26023,7 +26023,7 @@
         <v>2299</v>
       </c>
       <c r="J631" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="632" spans="1:10">
@@ -26366,7 +26366,7 @@
         <v>2286</v>
       </c>
       <c r="J642" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="643" spans="1:10">
@@ -26456,7 +26456,7 @@
         <v>2257</v>
       </c>
       <c r="J645" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="646" spans="1:10">
@@ -26610,7 +26610,7 @@
         <v>2284</v>
       </c>
       <c r="J650" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="651" spans="1:10">
@@ -26671,7 +26671,7 @@
         <v>2287</v>
       </c>
       <c r="J652" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="653" spans="1:10">
@@ -27121,7 +27121,7 @@
         <v>2304</v>
       </c>
       <c r="J667" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="668" spans="1:10">
@@ -27272,7 +27272,7 @@
         <v>2284</v>
       </c>
       <c r="J672" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="673" spans="1:10">
@@ -27565,7 +27565,7 @@
         <v>2301</v>
       </c>
       <c r="J682" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="683" spans="1:10">
@@ -27777,7 +27777,7 @@
         <v>2284</v>
       </c>
       <c r="J689" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="690" spans="1:10">
@@ -27899,7 +27899,7 @@
         <v>2284</v>
       </c>
       <c r="J693" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="694" spans="1:10">
@@ -28082,7 +28082,7 @@
         <v>2297</v>
       </c>
       <c r="J699" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="700" spans="1:10">
@@ -28111,7 +28111,7 @@
         <v>2295</v>
       </c>
       <c r="J700" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="701" spans="1:10">
@@ -28172,7 +28172,7 @@
         <v>2295</v>
       </c>
       <c r="J702" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="703" spans="1:10">
@@ -28201,7 +28201,7 @@
         <v>2292</v>
       </c>
       <c r="J703" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="704" spans="1:10">
@@ -28445,7 +28445,7 @@
         <v>2284</v>
       </c>
       <c r="J711" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="712" spans="1:10">
@@ -28605,7 +28605,7 @@
         <v>2284</v>
       </c>
       <c r="J716" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="717" spans="1:10">
@@ -28765,7 +28765,7 @@
         <v>2282</v>
       </c>
       <c r="J721" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="722" spans="1:10">
@@ -29047,7 +29047,7 @@
         <v>2284</v>
       </c>
       <c r="J730" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="731" spans="1:10">
@@ -29140,7 +29140,7 @@
         <v>2297</v>
       </c>
       <c r="J733" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="734" spans="1:10">
@@ -29381,7 +29381,7 @@
         <v>2295</v>
       </c>
       <c r="J741" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="742" spans="1:10">
@@ -29532,7 +29532,7 @@
         <v>2286</v>
       </c>
       <c r="J746" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="747" spans="1:10">
@@ -29718,7 +29718,7 @@
         <v>2282</v>
       </c>
       <c r="J752" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="753" spans="1:10">
@@ -29808,7 +29808,7 @@
         <v>2304</v>
       </c>
       <c r="J755" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="756" spans="1:10">
@@ -30084,7 +30084,7 @@
         <v>2295</v>
       </c>
       <c r="J764" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="765" spans="1:10">
@@ -30113,7 +30113,7 @@
         <v>2295</v>
       </c>
       <c r="J765" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="766" spans="1:10">
@@ -30424,7 +30424,7 @@
         <v>2288</v>
       </c>
       <c r="J775" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="776" spans="1:10">
@@ -30636,7 +30636,7 @@
         <v>2292</v>
       </c>
       <c r="J782" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="783" spans="1:10">
@@ -30851,7 +30851,7 @@
         <v>2303</v>
       </c>
       <c r="J789" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="790" spans="1:10">
@@ -31095,7 +31095,7 @@
         <v>2298</v>
       </c>
       <c r="J797" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="798" spans="1:10">
@@ -31182,7 +31182,7 @@
         <v>2291</v>
       </c>
       <c r="J800" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="801" spans="1:10">

--- a/report_cleansing_ps.xlsx
+++ b/report_cleansing_ps.xlsx
@@ -7971,7 +7971,7 @@
         <v>2274</v>
       </c>
       <c r="J23" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -8609,7 +8609,7 @@
         <v>2276</v>
       </c>
       <c r="J45" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -17275,7 +17275,7 @@
         <v>2288</v>
       </c>
       <c r="J343" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="344" spans="1:10">
@@ -17487,7 +17487,7 @@
         <v>2288</v>
       </c>
       <c r="J350" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="351" spans="1:10">
@@ -17667,7 +17667,7 @@
         <v>2292</v>
       </c>
       <c r="J356" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="357" spans="1:10">
@@ -18132,7 +18132,7 @@
         <v>2292</v>
       </c>
       <c r="J371" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="372" spans="1:10">
@@ -18559,7 +18559,7 @@
         <v>2282</v>
       </c>
       <c r="J385" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -19634,7 +19634,7 @@
         <v>2282</v>
       </c>
       <c r="J420" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="421" spans="1:10">
@@ -19913,7 +19913,7 @@
         <v>2284</v>
       </c>
       <c r="J429" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -20183,7 +20183,7 @@
         <v>2303</v>
       </c>
       <c r="J438" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="439" spans="1:10">
@@ -20308,7 +20308,7 @@
         <v>2288</v>
       </c>
       <c r="J442" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="443" spans="1:10">
@@ -20337,7 +20337,7 @@
         <v>2305</v>
       </c>
       <c r="J443" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="444" spans="1:10">
@@ -21609,7 +21609,7 @@
         <v>2288</v>
       </c>
       <c r="J485" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="486" spans="1:10">
@@ -22573,7 +22573,7 @@
         <v>2284</v>
       </c>
       <c r="J517" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="518" spans="1:10">
@@ -22840,7 +22840,7 @@
         <v>2288</v>
       </c>
       <c r="J526" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="527" spans="1:10">
@@ -25509,7 +25509,7 @@
         <v>2284</v>
       </c>
       <c r="J614" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="615" spans="1:10">
@@ -27272,7 +27272,7 @@
         <v>2284</v>
       </c>
       <c r="J672" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="673" spans="1:10">
@@ -27330,7 +27330,7 @@
         <v>2305</v>
       </c>
       <c r="J674" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="675" spans="1:10">
@@ -28352,7 +28352,7 @@
         <v>2291</v>
       </c>
       <c r="J708" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="709" spans="1:10">
@@ -28445,7 +28445,7 @@
         <v>2284</v>
       </c>
       <c r="J711" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="712" spans="1:10">
@@ -28890,7 +28890,7 @@
         <v>2304</v>
       </c>
       <c r="J725" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="726" spans="1:10">

--- a/report_cleansing_ps.xlsx
+++ b/report_cleansing_ps.xlsx
@@ -16091,7 +16091,7 @@
         <v>2274</v>
       </c>
       <c r="J303" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -17275,7 +17275,7 @@
         <v>2288</v>
       </c>
       <c r="J343" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="344" spans="1:10">
@@ -17487,7 +17487,7 @@
         <v>2288</v>
       </c>
       <c r="J350" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="351" spans="1:10">
@@ -18559,7 +18559,7 @@
         <v>2282</v>
       </c>
       <c r="J385" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -19634,7 +19634,7 @@
         <v>2282</v>
       </c>
       <c r="J420" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="421" spans="1:10">
@@ -19913,7 +19913,7 @@
         <v>2284</v>
       </c>
       <c r="J429" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -22573,7 +22573,7 @@
         <v>2284</v>
       </c>
       <c r="J517" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="518" spans="1:10">
@@ -22840,7 +22840,7 @@
         <v>2288</v>
       </c>
       <c r="J526" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="527" spans="1:10">
@@ -24231,7 +24231,7 @@
         <v>2300</v>
       </c>
       <c r="J572" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="573" spans="1:10">
@@ -24295,7 +24295,7 @@
         <v>2282</v>
       </c>
       <c r="J574" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="575" spans="1:10">
@@ -24356,7 +24356,7 @@
         <v>2282</v>
       </c>
       <c r="J576" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="577" spans="1:10">
@@ -25297,7 +25297,7 @@
         <v>2282</v>
       </c>
       <c r="J607" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="608" spans="1:10">
@@ -25509,7 +25509,7 @@
         <v>2284</v>
       </c>
       <c r="J614" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="615" spans="1:10">
@@ -27272,7 +27272,7 @@
         <v>2284</v>
       </c>
       <c r="J672" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="673" spans="1:10">
@@ -28765,7 +28765,7 @@
         <v>2282</v>
       </c>
       <c r="J721" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="722" spans="1:10">

--- a/report_cleansing_ps.xlsx
+++ b/report_cleansing_ps.xlsx
@@ -7971,7 +7971,7 @@
         <v>2274</v>
       </c>
       <c r="J23" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -8319,7 +8319,7 @@
         <v>2279</v>
       </c>
       <c r="J35" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -9334,7 +9334,7 @@
         <v>2274</v>
       </c>
       <c r="J70" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -9885,7 +9885,7 @@
         <v>2279</v>
       </c>
       <c r="J89" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -10987,7 +10987,7 @@
         <v>2279</v>
       </c>
       <c r="J127" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -11306,7 +11306,7 @@
         <v>2274</v>
       </c>
       <c r="J138" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -11683,7 +11683,7 @@
         <v>2279</v>
       </c>
       <c r="J151" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -12263,7 +12263,7 @@
         <v>2277</v>
       </c>
       <c r="J171" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -12321,7 +12321,7 @@
         <v>2274</v>
       </c>
       <c r="J173" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -12582,7 +12582,7 @@
         <v>2274</v>
       </c>
       <c r="J182" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -13336,7 +13336,7 @@
         <v>2274</v>
       </c>
       <c r="J208" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -13568,7 +13568,7 @@
         <v>2274</v>
       </c>
       <c r="J216" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -13742,7 +13742,7 @@
         <v>2279</v>
       </c>
       <c r="J222" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -14032,7 +14032,7 @@
         <v>2274</v>
       </c>
       <c r="J232" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -14322,7 +14322,7 @@
         <v>2274</v>
       </c>
       <c r="J242" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="243" spans="1:10">
@@ -14496,7 +14496,7 @@
         <v>2277</v>
       </c>
       <c r="J248" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="249" spans="1:10">
@@ -15076,7 +15076,7 @@
         <v>2277</v>
       </c>
       <c r="J268" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="269" spans="1:10">
@@ -15192,7 +15192,7 @@
         <v>2277</v>
       </c>
       <c r="J272" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="273" spans="1:10">
@@ -15279,7 +15279,7 @@
         <v>2274</v>
       </c>
       <c r="J275" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="276" spans="1:10">
@@ -15598,7 +15598,7 @@
         <v>2274</v>
       </c>
       <c r="J286" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="287" spans="1:10">
@@ -16352,7 +16352,7 @@
         <v>2274</v>
       </c>
       <c r="J312" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="313" spans="1:10">
@@ -17275,7 +17275,7 @@
         <v>2288</v>
       </c>
       <c r="J343" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="344" spans="1:10">
@@ -17307,7 +17307,7 @@
         <v>2282</v>
       </c>
       <c r="J344" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="345" spans="1:10">
@@ -17487,7 +17487,7 @@
         <v>2288</v>
       </c>
       <c r="J350" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="351" spans="1:10">
@@ -17667,7 +17667,7 @@
         <v>2292</v>
       </c>
       <c r="J356" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="357" spans="1:10">
@@ -18559,7 +18559,7 @@
         <v>2282</v>
       </c>
       <c r="J385" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -18588,7 +18588,7 @@
         <v>2292</v>
       </c>
       <c r="J386" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -19634,7 +19634,7 @@
         <v>2282</v>
       </c>
       <c r="J420" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="421" spans="1:10">
@@ -19913,7 +19913,7 @@
         <v>2284</v>
       </c>
       <c r="J429" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -20122,7 +20122,7 @@
         <v>2299</v>
       </c>
       <c r="J436" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="437" spans="1:10">
@@ -20276,7 +20276,7 @@
         <v>2284</v>
       </c>
       <c r="J441" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="442" spans="1:10">
@@ -20337,7 +20337,7 @@
         <v>2305</v>
       </c>
       <c r="J443" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="444" spans="1:10">
@@ -20613,7 +20613,7 @@
         <v>2304</v>
       </c>
       <c r="J452" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="453" spans="1:10">
@@ -21734,7 +21734,7 @@
         <v>2304</v>
       </c>
       <c r="J489" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="490" spans="1:10">
@@ -22573,7 +22573,7 @@
         <v>2284</v>
       </c>
       <c r="J517" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="518" spans="1:10">
@@ -22808,7 +22808,7 @@
         <v>2292</v>
       </c>
       <c r="J525" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="526" spans="1:10">
@@ -22840,7 +22840,7 @@
         <v>2288</v>
       </c>
       <c r="J526" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="527" spans="1:10">
@@ -22959,7 +22959,7 @@
         <v>2301</v>
       </c>
       <c r="J530" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="531" spans="1:10">
@@ -23293,7 +23293,7 @@
         <v>2299</v>
       </c>
       <c r="J541" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="542" spans="1:10">
@@ -24167,7 +24167,7 @@
         <v>2292</v>
       </c>
       <c r="J570" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="571" spans="1:10">
@@ -24199,7 +24199,7 @@
         <v>2296</v>
       </c>
       <c r="J571" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="572" spans="1:10">
@@ -24690,7 +24690,7 @@
         <v>2295</v>
       </c>
       <c r="J587" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="588" spans="1:10">
@@ -24844,7 +24844,7 @@
         <v>2284</v>
       </c>
       <c r="J592" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="593" spans="1:10">
@@ -25448,7 +25448,7 @@
         <v>2304</v>
       </c>
       <c r="J612" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="613" spans="1:10">
@@ -25509,7 +25509,7 @@
         <v>2284</v>
       </c>
       <c r="J614" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="615" spans="1:10">
@@ -26023,7 +26023,7 @@
         <v>2299</v>
       </c>
       <c r="J631" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="632" spans="1:10">
@@ -26366,7 +26366,7 @@
         <v>2286</v>
       </c>
       <c r="J642" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="643" spans="1:10">
@@ -27121,7 +27121,7 @@
         <v>2304</v>
       </c>
       <c r="J667" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="668" spans="1:10">
@@ -27272,7 +27272,7 @@
         <v>2284</v>
       </c>
       <c r="J672" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="673" spans="1:10">
@@ -27330,7 +27330,7 @@
         <v>2305</v>
       </c>
       <c r="J674" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="675" spans="1:10">
@@ -27565,7 +27565,7 @@
         <v>2301</v>
       </c>
       <c r="J682" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="683" spans="1:10">
@@ -28201,7 +28201,7 @@
         <v>2292</v>
       </c>
       <c r="J703" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="704" spans="1:10">
@@ -28352,7 +28352,7 @@
         <v>2291</v>
       </c>
       <c r="J708" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="709" spans="1:10">
@@ -28890,7 +28890,7 @@
         <v>2304</v>
       </c>
       <c r="J725" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="726" spans="1:10">
@@ -29808,7 +29808,7 @@
         <v>2304</v>
       </c>
       <c r="J755" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="756" spans="1:10">

--- a/report_cleansing_ps.xlsx
+++ b/report_cleansing_ps.xlsx
@@ -15580,7 +15580,7 @@
         <v>3083</v>
       </c>
       <c r="J202" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="203" spans="1:10">
@@ -16566,7 +16566,7 @@
         <v>3083</v>
       </c>
       <c r="J236" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="237" spans="1:10">
@@ -16653,7 +16653,7 @@
         <v>3083</v>
       </c>
       <c r="J239" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="240" spans="1:10">
@@ -17204,7 +17204,7 @@
         <v>3083</v>
       </c>
       <c r="J258" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="259" spans="1:10">
@@ -23713,7 +23713,7 @@
         <v>3089</v>
       </c>
       <c r="J481" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="482" spans="1:10">
@@ -25927,7 +25927,7 @@
         <v>3092</v>
       </c>
       <c r="J553" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="554" spans="1:10">
@@ -26354,7 +26354,7 @@
         <v>3096</v>
       </c>
       <c r="J567" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="568" spans="1:10">
@@ -27719,7 +27719,7 @@
         <v>3096</v>
       </c>
       <c r="J612" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="613" spans="1:10">
@@ -31070,7 +31070,7 @@
         <v>3104</v>
       </c>
       <c r="J723" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="724" spans="1:10">
@@ -31189,7 +31189,7 @@
         <v>3106</v>
       </c>
       <c r="J727" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="728" spans="1:10">
@@ -34253,7 +34253,7 @@
         <v>3092</v>
       </c>
       <c r="J828" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="829" spans="1:10">
@@ -34465,7 +34465,7 @@
         <v>3104</v>
       </c>
       <c r="J835" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="836" spans="1:10">
@@ -34494,7 +34494,7 @@
         <v>3102</v>
       </c>
       <c r="J836" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="837" spans="1:10">
@@ -34555,7 +34555,7 @@
         <v>3102</v>
       </c>
       <c r="J838" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="839" spans="1:10">
@@ -39320,7 +39320,7 @@
         <v>3100</v>
       </c>
       <c r="J993" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="994" spans="1:10">
@@ -39410,7 +39410,7 @@
         <v>3104</v>
       </c>
       <c r="J996" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="997" spans="1:10">
@@ -39872,7 +39872,7 @@
         <v>3096</v>
       </c>
       <c r="J1011" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="1012" spans="1:10">
@@ -40020,7 +40020,7 @@
         <v>3113</v>
       </c>
       <c r="J1016" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="1017" spans="1:10">
@@ -42353,7 +42353,7 @@
         <v>3100</v>
       </c>
       <c r="J1092" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="1093" spans="1:10">
@@ -42713,7 +42713,7 @@
         <v>3100</v>
       </c>
       <c r="J1104" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
   </sheetData>

--- a/report_cleansing_ps.xlsx
+++ b/report_cleansing_ps.xlsx
@@ -17845,7 +17845,7 @@
         <v>3405</v>
       </c>
       <c r="J247" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="248" spans="1:10">
@@ -19411,7 +19411,7 @@
         <v>3405</v>
       </c>
       <c r="J301" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="302" spans="1:10">
@@ -20223,7 +20223,7 @@
         <v>3402</v>
       </c>
       <c r="J329" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="330" spans="1:10">
@@ -22166,7 +22166,7 @@
         <v>3402</v>
       </c>
       <c r="J396" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="397" spans="1:10">
@@ -26730,7 +26730,7 @@
         <v>3410</v>
       </c>
       <c r="J551" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="552" spans="1:10">
@@ -30959,7 +30959,7 @@
         <v>3415</v>
       </c>
       <c r="J690" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="691" spans="1:10">
@@ -39147,7 +39147,7 @@
         <v>3410</v>
       </c>
       <c r="J959" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="960" spans="1:10">
@@ -39577,7 +39577,7 @@
         <v>3422</v>
       </c>
       <c r="J973" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="974" spans="1:10">
@@ -40068,7 +40068,7 @@
         <v>3416</v>
       </c>
       <c r="J989" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="990" spans="1:10">
